--- a/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>usb type c 25w</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -622,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +737,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>12</v>

--- a/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
@@ -99,7 +99,7 @@
     <t>usb type c 25w</t>
   </si>
   <si>
-    <t>2026-08-02</t>
+    <t>2026-08-07</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
@@ -99,7 +99,7 @@
     <t>usb type c 25w</t>
   </si>
   <si>
-    <t>2026-08-07</t>
+    <t>2026-08-08</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
@@ -99,7 +99,7 @@
     <t>usb type c 25w</t>
   </si>
   <si>
-    <t>2026-08-08</t>
+    <t>2026-08-11</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="L3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/accessory-sell-and-fixes/downloaded-inventory-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -51,6 +51,9 @@
     <t>Age (days)</t>
   </si>
   <si>
+    <t>Return Date</t>
+  </si>
+  <si>
     <t>2026-07-28</t>
   </si>
   <si>
@@ -99,7 +102,7 @@
     <t>usb type c 25w</t>
   </si>
   <si>
-    <t>2026-08-11</t>
+    <t>2026-09-09</t>
   </si>
 </sst>
 </file>
@@ -504,17 +507,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,85 +554,94 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
       <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
       </c>
       <c r="I3">
         <v>145</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -637,17 +649,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -684,9 +696,12 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -705,19 +720,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>8</v>
@@ -728,16 +743,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>12</v>
@@ -746,7 +761,7 @@
         <v>4.25</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
